--- a/Topic Relevant Comments - Nigeria/Wizarab/Sex Toys and Raping Young Boys.xlsx
+++ b/Topic Relevant Comments - Nigeria/Wizarab/Sex Toys and Raping Young Boys.xlsx
@@ -88,24 +88,24 @@
     <t>Alot of these boys were molested by close relatives. Stories choke.</t>
   </si>
   <si>
+    <t>Really really sad When you research about young boys who have been molested, it's not a joke if you truly have humanity in you, you will weep. The same way we feel sad for the girls, I bet it wirh you the boy child own is more sad. Imagine putting a four years old to either lick you down there or suck you up there, wo onikureeeee all of you that have ever done this. You were possessed by your wicked and pervert thoughts. You purnish them so much that it becomes mastered in their thoughts then some either starts to masturbate or just become something else As if that's not enough, you deny them of freedom around adults. You put fear in them, deny them of innocent childhood The annoying thing is that we've so many people online reading this and already plotting evil on the next child to use, and tactics to use. The wrath of God will visit you. You will be caught and disgraced. Parents, caregivers, Nannie's do what is right don't get caught up in your own desires and be involved in evil. That you will not pay for it forget about it you will because you will definitely give an account of yourself.</t>
+  </si>
+  <si>
     <t>Men enjoy it is the reason why they don't report or talk about it. We don't have cases like this reported to station, and no NGO is taking it as a cause for concern. This is what the former PRO said and it got me thinking that, do men get justice for anything at all? Hell No, and we still get backlash for every single thing.</t>
   </si>
   <si>
-    <t>Really really sad When you research about young boys who have been molested, it's not a joke if you truly have humanity in you, you will weep. The same way we feel sad for the girls, I bet it wirh you the boy child own is more sad. Imagine putting a four years old to either lick you down there or suck you up there, wo onikureeeee all of you that have ever done this. You were possessed by your wicked and pervert thoughts. You purnish them so much that it becomes mastered in their thoughts then some either starts to masturbate or just become something else As if that's not enough, you deny them of freedom around adults. You put fear in them, deny them of innocent childhood The annoying thing is that we've so many people online reading this and already plotting evil on the next child to use, and tactics to use. The wrath of God will visit you. You will be caught and disgraced. Parents, caregivers, Nannie's do what is right don't get caught up in your own desires and be involved in evil. That you will not pay for it forget about it you will because you will definitely give an account of yourself.</t>
-  </si>
-  <si>
     <t>Justice for the boy child, dont be an apologist.</t>
   </si>
   <si>
+    <t>Don't u think if male Victims felt safe to speak up, we could have clearer data.</t>
+  </si>
+  <si>
     <t>Why do you think boys don't speak up about this?</t>
   </si>
   <si>
     <t>That claim is serious and shouldn't be thrown around casually. Sexual abuse is wrong regardless of gender, and real discussions need verified facts not harmful generalizations. If you're talking about abuse, it deserves sensitivity and evidence, not statistics without sources.</t>
   </si>
   <si>
-    <t>Don't u think if male Victims felt safe to speak up, we could have clearer data.</t>
-  </si>
-  <si>
     <t>People don't understand the molestation that has happened between men from 5 -15 from older women who should have known better Rape is not a male problem but a gender issue</t>
   </si>
   <si>
@@ -217,12 +217,12 @@
     <t>Yes,the focus is mainly on the female gender most times</t>
   </si>
   <si>
+    <t>So now you know it's dangerous. When women claim all of them have been raped or sexually assaulted. We don't hear the statistics. When they say men are rapists, we don't hear statistics. It's now you want to challenge statistics</t>
+  </si>
+  <si>
     <t>Men don't attach emotions to many hints, they could experience terrible things but know how to put it behind them and move forward very quickly. A man would be going through tough times and be smiling and all happy</t>
   </si>
   <si>
-    <t>So now you know it's dangerous. When women claim all of them have been raped or sexually assaulted. We don't hear the statistics. When they say men are rapists, we don't hear statistics. It's now you want to challenge statistics</t>
-  </si>
-  <si>
     <t>90% of them have a sex toy right now, this is proof that all you said is true when there was none. They dealt with little boys.</t>
   </si>
   <si>
@@ -289,18 +289,21 @@
     <t>Many young guys were disvirg*n by bis sister in the environment they're living together,in the name of I will buy you sweet, don't tell anyone.</t>
   </si>
   <si>
+    <t>They started off with "my husband". Never allow any fool to call your child "my husband".</t>
+  </si>
+  <si>
     <t>You will experience this, if you don't your children will! Then we can ask you where you got your statistics. Stupid, nonsensical, fuulish thing</t>
   </si>
   <si>
-    <t>They started off with "my husband". Never allow any fool to call your child "my husband".</t>
-  </si>
-  <si>
     <t>I don't think it is a lack of sex toys because currently,not all ladies are with sex toys.</t>
   </si>
   <si>
     <t>Oga he's wrong</t>
   </si>
   <si>
+    <t>E get as the thing be bros</t>
+  </si>
+  <si>
     <t>No one dares that shit with my kids. You are not even allowed to use fine boy or fine girl</t>
   </si>
   <si>
@@ -313,6 +316,9 @@
     <t>Exactly why they don't take us seriously. Because of this. At that age it wasn't anything fun.</t>
   </si>
   <si>
+    <t>The world don't care</t>
+  </si>
+  <si>
     <t>If men start to speak up on this issue,80% of men were molested at a very young age but we're not ready for this discussion</t>
   </si>
   <si>
@@ -385,6 +391,9 @@
     <t>I can say that I'm a victim here But thank God my past didnt have a toll on my life Make lying dog just keep on lying sha ‍↕️</t>
   </si>
   <si>
+    <t>How will your d1ck stand when you are not in the mood? Your d1ck need to stand for you to be rap£d.. Someone should educate me please</t>
+  </si>
+  <si>
     <t>I think men should start getting sex toys also</t>
   </si>
   <si>
@@ -562,9 +571,15 @@
     <t>Do your own research and bring the data</t>
   </si>
   <si>
+    <t>Na that person wey invent the sex toys I wan catch</t>
+  </si>
+  <si>
     <t>I hope you've gotten over it</t>
   </si>
   <si>
+    <t>Omo it is well.. hope you okay gee?</t>
+  </si>
+  <si>
     <t>I nearly insulted you until I finished reading</t>
   </si>
   <si>
@@ -602,21 +617,6 @@
   </si>
   <si>
     <t>I could remember what happened in QRC onitsha Anambra many years ago. That 6 girls r@ped a man selling ICE cream to the point the man fainted. The story passed along so many sets then. That school is a bunch of horny girls. If lesbian are 100 in Anambra 70 are from QRC.</t>
-  </si>
-  <si>
-    <t>E get as the thing be bros</t>
-  </si>
-  <si>
-    <t>Its retarded. Don't worry - its not you, its them.</t>
-  </si>
-  <si>
-    <t>Don't say that</t>
-  </si>
-  <si>
-    <t>Oga you dey mad?</t>
-  </si>
-  <si>
-    <t>The world don't care</t>
   </si>
 </sst>
 </file>
